--- a/data/trans_orig/P16B13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19276</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27303</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,97 +845,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1666</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1744</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1794</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>23061</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24073</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50197</t>
+          <t>50617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58195</t>
+          <t>58104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29484</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>56122</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1531,97 +1531,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1753</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16040</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>30851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>60409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>108176</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28384</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32385</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60241</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,62 +2827,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31958</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86615</t>
+          <t>85161</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,62 +3170,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2108</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>7988</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6534</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20789</t>
+          <t>21374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57150</t>
+          <t>57368</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64527</t>
+          <t>64538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8285</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27965</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40045</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90832</t>
+          <t>90390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103994</t>
+          <t>103910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13968</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5879</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182076</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189201</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>322831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016 (tasa de respuesta: 97,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15805</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29906</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46826</t>
+          <t>46942</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,62 +4774,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1851</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8785</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1851</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>8901</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>20632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>26444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33626</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51224</t>
+          <t>51730</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61630</t>
+          <t>61659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11394</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>16756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>44205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,62 +5460,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1166</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6025</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>19000</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61081</t>
+          <t>61773</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6190</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96038</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218352</t>
+          <t>218348</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232463</t>
+          <t>232777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P16B13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Habitat-trans_orig.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23061</t>
+          <t>22856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23536</t>
+          <t>24351</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50617</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58104</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6252</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8804</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>15735</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30851</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>38066</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>60409</t>
+          <t>60351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>84579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200197</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27620</t>
+          <t>27738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60202</t>
+          <t>60069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>32911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85161</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6099</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>6183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21374</t>
+          <t>21681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>33530</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57368</t>
+          <t>57295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64538</t>
+          <t>64525</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27786</t>
+          <t>28256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39912</t>
+          <t>40034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59736</t>
+          <t>59833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90390</t>
+          <t>89644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>103910</t>
+          <t>103952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14147</t>
+          <t>13677</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>182299</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>189200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306978</t>
+          <t>306537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>322831</t>
+          <t>322736</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>14528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46942</t>
+          <t>46813</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -4969,7 +4969,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20632</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26444</t>
+          <t>26492</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33576</t>
+          <t>33585</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51730</t>
+          <t>52634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61659</t>
+          <t>61678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>44026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>39472</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61773</t>
+          <t>61058</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4802</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5823,7 +5823,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218348</t>
+          <t>218329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232777</t>
+          <t>232549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
